--- a/media/Levels/Level_1.xlsx
+++ b/media/Levels/Level_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B59163A-0A03-4DA7-9E33-4839FF2F3A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E66378-39B1-42AF-A0F1-5DF32260253A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3876" yWindow="192" windowWidth="13836" windowHeight="12156" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="2508" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,10 +33,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -754,16 +750,16 @@
         <v>0</v>
       </c>
       <c r="S3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS3" s="1">
         <v>0</v>
@@ -814,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV6" s="1">
         <v>0</v>
@@ -874,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV9" s="1">
         <v>0</v>
@@ -958,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR12" s="3">
         <v>0</v>
@@ -991,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="CD12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV12" s="1">
         <v>0</v>
@@ -2921,10 +2917,10 @@
         <v>0</v>
       </c>
       <c r="AF26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY26" s="2">
         <v>0</v>
@@ -3323,10 +3319,10 @@
         <v>0</v>
       </c>
       <c r="AF29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY29" s="2">
         <v>0</v>
@@ -3725,10 +3721,10 @@
         <v>0</v>
       </c>
       <c r="AF32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY32" s="2">
         <v>0</v>
@@ -3965,10 +3961,10 @@
         <v>0</v>
       </c>
       <c r="AF35" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ35" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV35" s="1">
         <v>0</v>
@@ -4007,10 +4003,10 @@
         <v>0</v>
       </c>
       <c r="AF38" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ38" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV38" s="1">
         <v>0</v>
@@ -4049,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="AF41" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO41" s="2">
         <v>0</v>
@@ -4112,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="BQ41" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV41" s="1">
         <v>0</v>
@@ -4346,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="AF44" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO44" s="2">
         <v>0</v>
@@ -4409,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="BQ44" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX44" s="3">
         <v>0</v>
@@ -5354,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="AF56" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO56" s="2">
         <v>0</v>
@@ -5417,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="BQ56" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CL56" s="3">
         <v>0</v>
@@ -5666,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="AF59" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO59" s="2">
         <v>0</v>
@@ -5729,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="BQ59" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CL59" s="3">
         <v>0</v>
@@ -5843,10 +5839,10 @@
         <v>0</v>
       </c>
       <c r="AF62" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ62" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV62" s="1">
         <v>0</v>
@@ -5885,10 +5881,10 @@
         <v>0</v>
       </c>
       <c r="AF65" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ65" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV65" s="1">
         <v>0</v>
@@ -5996,10 +5992,10 @@
         <v>0</v>
       </c>
       <c r="AF68" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ68" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY68" s="2">
         <v>0</v>
@@ -6407,10 +6403,10 @@
         <v>0</v>
       </c>
       <c r="AF71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY71" s="2">
         <v>0</v>
@@ -6809,10 +6805,10 @@
         <v>0</v>
       </c>
       <c r="AF74" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BQ74" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY74" s="2">
         <v>0</v>
@@ -8870,7 +8866,7 @@
         <v>0</v>
       </c>
       <c r="S89" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS89" s="3">
         <v>0</v>
@@ -8903,7 +8899,7 @@
         <v>0</v>
       </c>
       <c r="CD89" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV89" s="1">
         <v>0</v>
@@ -8978,16 +8974,16 @@
         <v>0</v>
       </c>
       <c r="S92" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU92" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC92" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD92" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV92" s="1">
         <v>0</v>
@@ -9038,16 +9034,16 @@
         <v>0</v>
       </c>
       <c r="S95" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU95" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC95" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD95" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV95" s="1">
         <v>0</v>
@@ -9098,16 +9094,16 @@
         <v>0</v>
       </c>
       <c r="S98" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU98" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC98" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD98" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS98" s="1">
         <v>0</v>

--- a/media/Levels/Level_1.xlsx
+++ b/media/Levels/Level_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E66378-39B1-42AF-A0F1-5DF32260253A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5D7F7C-0C78-4BC1-A19C-CFFF9176399C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2508" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="3672" yWindow="84" windowWidth="13836" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -729,7 +729,7 @@
       <c r="E2" s="1">
         <v>5</v>
       </c>
-      <c r="S2" s="1">
+      <c r="N2" s="1">
         <v>0</v>
       </c>
       <c r="AT2" s="1">
@@ -738,7 +738,7 @@
       <c r="BB2" s="1">
         <v>0</v>
       </c>
-      <c r="CD2" s="1">
+      <c r="CI2" s="1">
         <v>0</v>
       </c>
       <c r="CR2" s="1">
@@ -749,7 +749,7 @@
       <c r="D3" s="1">
         <v>0</v>
       </c>
-      <c r="S3" s="1">
+      <c r="N3" s="1">
         <v>4</v>
       </c>
       <c r="AT3" s="1">
@@ -758,7 +758,7 @@
       <c r="BB3" s="1">
         <v>4</v>
       </c>
-      <c r="CD3" s="1">
+      <c r="CI3" s="1">
         <v>4</v>
       </c>
       <c r="CS3" s="1">
@@ -769,7 +769,7 @@
       <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="S4" s="1">
+      <c r="N4" s="1">
         <v>0</v>
       </c>
       <c r="AT4" s="1">
@@ -778,7 +778,7 @@
       <c r="BB4" s="1">
         <v>0</v>
       </c>
-      <c r="CD4" s="1">
+      <c r="CI4" s="1">
         <v>0</v>
       </c>
       <c r="CT4" s="1">
@@ -789,7 +789,7 @@
       <c r="B5" s="1">
         <v>5</v>
       </c>
-      <c r="S5" s="1">
+      <c r="N5" s="4">
         <v>0</v>
       </c>
       <c r="AT5" s="1">
@@ -798,7 +798,7 @@
       <c r="BB5" s="1">
         <v>0</v>
       </c>
-      <c r="CD5" s="1">
+      <c r="CI5" s="4">
         <v>0</v>
       </c>
       <c r="CU5" s="1">
@@ -809,8 +809,8 @@
       <c r="A6" s="1">
         <v>0</v>
       </c>
-      <c r="S6" s="1">
-        <v>4</v>
+      <c r="N6" s="4">
+        <v>8</v>
       </c>
       <c r="AT6" s="1">
         <v>4</v>
@@ -818,8 +818,8 @@
       <c r="BB6" s="1">
         <v>4</v>
       </c>
-      <c r="CD6" s="1">
-        <v>4</v>
+      <c r="CI6" s="4">
+        <v>8</v>
       </c>
       <c r="CV6" s="1">
         <v>0</v>
@@ -829,7 +829,7 @@
       <c r="A7" s="1">
         <v>0</v>
       </c>
-      <c r="S7" s="1">
+      <c r="N7" s="4">
         <v>0</v>
       </c>
       <c r="AT7" s="1">
@@ -838,7 +838,7 @@
       <c r="BB7" s="1">
         <v>0</v>
       </c>
-      <c r="CD7" s="1">
+      <c r="CI7" s="4">
         <v>0</v>
       </c>
       <c r="CV7" s="1">
@@ -849,7 +849,7 @@
       <c r="A8" s="1">
         <v>0</v>
       </c>
-      <c r="S8" s="1">
+      <c r="N8" s="4">
         <v>0</v>
       </c>
       <c r="AT8" s="1">
@@ -858,7 +858,7 @@
       <c r="BB8" s="1">
         <v>0</v>
       </c>
-      <c r="CD8" s="1">
+      <c r="CI8" s="4">
         <v>0</v>
       </c>
       <c r="CV8" s="1">
@@ -869,8 +869,8 @@
       <c r="A9" s="1">
         <v>0</v>
       </c>
-      <c r="S9" s="1">
-        <v>4</v>
+      <c r="N9" s="4">
+        <v>8</v>
       </c>
       <c r="AT9" s="1">
         <v>4</v>
@@ -878,8 +878,8 @@
       <c r="BB9" s="1">
         <v>4</v>
       </c>
-      <c r="CD9" s="1">
-        <v>4</v>
+      <c r="CI9" s="4">
+        <v>8</v>
       </c>
       <c r="CV9" s="1">
         <v>0</v>
@@ -889,7 +889,7 @@
       <c r="A10" s="1">
         <v>0</v>
       </c>
-      <c r="S10" s="1">
+      <c r="N10" s="4">
         <v>0</v>
       </c>
       <c r="AT10" s="1">
@@ -898,7 +898,7 @@
       <c r="BB10" s="1">
         <v>0</v>
       </c>
-      <c r="CD10" s="1">
+      <c r="CI10" s="4">
         <v>0</v>
       </c>
       <c r="CV10" s="1">
@@ -909,7 +909,7 @@
       <c r="A11" s="1">
         <v>0</v>
       </c>
-      <c r="S11" s="1">
+      <c r="N11" s="1">
         <v>0</v>
       </c>
       <c r="AR11" s="3">
@@ -942,7 +942,7 @@
       <c r="BD11" s="3">
         <v>0</v>
       </c>
-      <c r="CD11" s="1">
+      <c r="CI11" s="1">
         <v>0</v>
       </c>
       <c r="CV11" s="1">
@@ -953,7 +953,7 @@
       <c r="A12" s="1">
         <v>0</v>
       </c>
-      <c r="S12" s="1">
+      <c r="N12" s="1">
         <v>4</v>
       </c>
       <c r="AR12" s="3">
@@ -986,7 +986,7 @@
       <c r="BD12" s="3">
         <v>0</v>
       </c>
-      <c r="CD12" s="1">
+      <c r="CI12" s="1">
         <v>4</v>
       </c>
       <c r="CV12" s="1">
@@ -997,7 +997,7 @@
       <c r="A13" s="1">
         <v>0</v>
       </c>
-      <c r="S13" s="1">
+      <c r="N13" s="1">
         <v>0</v>
       </c>
       <c r="AR13" s="3">
@@ -1039,7 +1039,7 @@
       <c r="BD13" s="3">
         <v>0</v>
       </c>
-      <c r="CD13" s="1">
+      <c r="CI13" s="1">
         <v>0</v>
       </c>
       <c r="CV13" s="1">
@@ -1050,6 +1050,15 @@
       <c r="A14" s="1">
         <v>0</v>
       </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
       <c r="E14" s="2">
         <v>0</v>
       </c>
@@ -1101,15 +1110,6 @@
       <c r="U14" s="2">
         <v>0</v>
       </c>
-      <c r="V14" s="2">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2">
-        <v>0</v>
-      </c>
-      <c r="X14" s="2">
-        <v>0</v>
-      </c>
       <c r="AR14" s="3">
         <v>0</v>
       </c>
@@ -1140,15 +1140,6 @@
       <c r="BD14" s="3">
         <v>0</v>
       </c>
-      <c r="BY14" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ14" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA14" s="2">
-        <v>0</v>
-      </c>
       <c r="CB14" s="2">
         <v>0</v>
       </c>
@@ -1198,6 +1189,15 @@
         <v>0</v>
       </c>
       <c r="CR14" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS14" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT14" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU14" s="2">
         <v>0</v>
       </c>
       <c r="CV14" s="1">
@@ -1208,6 +1208,15 @@
       <c r="A15" s="1">
         <v>0</v>
       </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
       <c r="E15" s="2">
         <v>0</v>
       </c>
@@ -1259,15 +1268,6 @@
       <c r="U15" s="2">
         <v>0</v>
       </c>
-      <c r="V15" s="2">
-        <v>0</v>
-      </c>
-      <c r="W15" s="2">
-        <v>0</v>
-      </c>
-      <c r="X15" s="2">
-        <v>0</v>
-      </c>
       <c r="AR15" s="3">
         <v>0</v>
       </c>
@@ -1298,15 +1298,6 @@
       <c r="BD15" s="3">
         <v>0</v>
       </c>
-      <c r="BY15" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ15" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA15" s="2">
-        <v>0</v>
-      </c>
       <c r="CB15" s="2">
         <v>0</v>
       </c>
@@ -1356,6 +1347,15 @@
         <v>0</v>
       </c>
       <c r="CR15" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS15" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT15" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU15" s="2">
         <v>0</v>
       </c>
       <c r="CV15" s="1">
@@ -1366,6 +1366,15 @@
       <c r="A16" s="1">
         <v>0</v>
       </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
@@ -1417,24 +1426,6 @@
       <c r="U16" s="2">
         <v>0</v>
       </c>
-      <c r="V16" s="2">
-        <v>0</v>
-      </c>
-      <c r="W16" s="2">
-        <v>0</v>
-      </c>
-      <c r="X16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA16" s="2">
-        <v>0</v>
-      </c>
       <c r="CB16" s="2">
         <v>0</v>
       </c>
@@ -1484,6 +1475,15 @@
         <v>0</v>
       </c>
       <c r="CR16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU16" s="2">
         <v>0</v>
       </c>
       <c r="CV16" s="1">
@@ -1494,6 +1494,15 @@
       <c r="A17" s="1">
         <v>0</v>
       </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
       <c r="E17" s="2">
         <v>0</v>
       </c>
@@ -1545,24 +1554,6 @@
       <c r="U17" s="2">
         <v>0</v>
       </c>
-      <c r="V17" s="2">
-        <v>0</v>
-      </c>
-      <c r="W17" s="2">
-        <v>0</v>
-      </c>
-      <c r="X17" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY17" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ17" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA17" s="2">
-        <v>0</v>
-      </c>
       <c r="CB17" s="2">
         <v>0</v>
       </c>
@@ -1612,6 +1603,15 @@
         <v>0</v>
       </c>
       <c r="CR17" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS17" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT17" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU17" s="2">
         <v>0</v>
       </c>
       <c r="CV17" s="1">
@@ -1622,6 +1622,15 @@
       <c r="A18" s="1">
         <v>0</v>
       </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
       <c r="E18" s="2">
         <v>0</v>
       </c>
@@ -1673,24 +1682,6 @@
       <c r="U18" s="2">
         <v>0</v>
       </c>
-      <c r="V18" s="2">
-        <v>0</v>
-      </c>
-      <c r="W18" s="2">
-        <v>0</v>
-      </c>
-      <c r="X18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY18" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ18" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA18" s="2">
-        <v>0</v>
-      </c>
       <c r="CB18" s="2">
         <v>0</v>
       </c>
@@ -1740,6 +1731,15 @@
         <v>0</v>
       </c>
       <c r="CR18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT18" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU18" s="2">
         <v>0</v>
       </c>
       <c r="CV18" s="1">
@@ -1750,6 +1750,15 @@
       <c r="A19" s="1">
         <v>0</v>
       </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
       <c r="E19" s="2">
         <v>0</v>
       </c>
@@ -1801,24 +1810,6 @@
       <c r="U19" s="2">
         <v>0</v>
       </c>
-      <c r="V19" s="2">
-        <v>0</v>
-      </c>
-      <c r="W19" s="2">
-        <v>0</v>
-      </c>
-      <c r="X19" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY19" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ19" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA19" s="2">
-        <v>0</v>
-      </c>
       <c r="CB19" s="2">
         <v>0</v>
       </c>
@@ -1868,6 +1859,15 @@
         <v>0</v>
       </c>
       <c r="CR19" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS19" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT19" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU19" s="2">
         <v>0</v>
       </c>
       <c r="CV19" s="1">
@@ -1878,6 +1878,15 @@
       <c r="A20" s="1">
         <v>0</v>
       </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
       <c r="E20" s="2">
         <v>0</v>
       </c>
@@ -1929,15 +1938,6 @@
       <c r="U20" s="2">
         <v>0</v>
       </c>
-      <c r="V20" s="2">
-        <v>0</v>
-      </c>
-      <c r="W20" s="2">
-        <v>0</v>
-      </c>
-      <c r="X20" s="2">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1968,15 +1968,6 @@
       <c r="BS20" s="3">
         <v>0</v>
       </c>
-      <c r="BY20" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ20" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA20" s="2">
-        <v>0</v>
-      </c>
       <c r="CB20" s="2">
         <v>0</v>
       </c>
@@ -2026,6 +2017,15 @@
         <v>0</v>
       </c>
       <c r="CR20" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS20" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT20" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU20" s="2">
         <v>0</v>
       </c>
       <c r="CV20" s="1">
@@ -2036,6 +2036,15 @@
       <c r="A21" s="1">
         <v>0</v>
       </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
       <c r="E21" s="2">
         <v>0</v>
       </c>
@@ -2087,15 +2096,6 @@
       <c r="U21" s="2">
         <v>0</v>
       </c>
-      <c r="V21" s="2">
-        <v>0</v>
-      </c>
-      <c r="W21" s="2">
-        <v>0</v>
-      </c>
-      <c r="X21" s="2">
-        <v>0</v>
-      </c>
       <c r="AD21" s="3">
         <v>0</v>
       </c>
@@ -2126,15 +2126,6 @@
       <c r="BS21" s="3">
         <v>0</v>
       </c>
-      <c r="BY21" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ21" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA21" s="2">
-        <v>0</v>
-      </c>
       <c r="CB21" s="2">
         <v>0</v>
       </c>
@@ -2184,6 +2175,15 @@
         <v>0</v>
       </c>
       <c r="CR21" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS21" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT21" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU21" s="2">
         <v>0</v>
       </c>
       <c r="CV21" s="1">
@@ -2194,6 +2194,15 @@
       <c r="A22" s="1">
         <v>0</v>
       </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
@@ -2243,15 +2252,6 @@
         <v>0</v>
       </c>
       <c r="U22" s="2">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2">
-        <v>0</v>
-      </c>
-      <c r="W22" s="2">
-        <v>0</v>
-      </c>
-      <c r="X22" s="2">
         <v>0</v>
       </c>
       <c r="AD22" s="3">
@@ -2338,15 +2338,6 @@
       <c r="BS22" s="3">
         <v>0</v>
       </c>
-      <c r="BY22" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ22" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA22" s="2">
-        <v>0</v>
-      </c>
       <c r="CB22" s="2">
         <v>0</v>
       </c>
@@ -2396,6 +2387,15 @@
         <v>0</v>
       </c>
       <c r="CR22" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS22" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT22" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU22" s="2">
         <v>0</v>
       </c>
       <c r="CV22" s="1">
@@ -2406,6 +2406,15 @@
       <c r="A23" s="1">
         <v>0</v>
       </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
       <c r="E23" s="2">
         <v>0</v>
       </c>
@@ -2428,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
@@ -2437,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P23" s="2">
         <v>0</v>
@@ -2457,15 +2466,6 @@
       <c r="U23" s="2">
         <v>0</v>
       </c>
-      <c r="V23" s="2">
-        <v>0</v>
-      </c>
-      <c r="W23" s="2">
-        <v>0</v>
-      </c>
-      <c r="X23" s="2">
-        <v>0</v>
-      </c>
       <c r="AD23" s="3">
         <v>0</v>
       </c>
@@ -2496,15 +2496,6 @@
       <c r="BS23" s="3">
         <v>0</v>
       </c>
-      <c r="BY23" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ23" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA23" s="2">
-        <v>0</v>
-      </c>
       <c r="CB23" s="2">
         <v>0</v>
       </c>
@@ -2527,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="CI23" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CJ23" s="2">
         <v>0</v>
@@ -2536,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="CL23" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CM23" s="2">
         <v>0</v>
@@ -2554,6 +2545,15 @@
         <v>0</v>
       </c>
       <c r="CR23" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS23" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT23" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU23" s="2">
         <v>0</v>
       </c>
       <c r="CV23" s="1">
@@ -2564,6 +2564,15 @@
       <c r="A24" s="1">
         <v>0</v>
       </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
@@ -2615,15 +2624,6 @@
       <c r="U24" s="2">
         <v>0</v>
       </c>
-      <c r="V24" s="2">
-        <v>0</v>
-      </c>
-      <c r="W24" s="2">
-        <v>0</v>
-      </c>
-      <c r="X24" s="2">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
@@ -2654,15 +2654,6 @@
       <c r="BS24" s="3">
         <v>0</v>
       </c>
-      <c r="BY24" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ24" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA24" s="2">
-        <v>0</v>
-      </c>
       <c r="CB24" s="2">
         <v>0</v>
       </c>
@@ -2712,6 +2703,15 @@
         <v>0</v>
       </c>
       <c r="CR24" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS24" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT24" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU24" s="2">
         <v>0</v>
       </c>
       <c r="CV24" s="1">
@@ -2722,6 +2722,15 @@
       <c r="A25" s="1">
         <v>0</v>
       </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
       <c r="E25" s="2">
         <v>0</v>
       </c>
@@ -2773,30 +2782,12 @@
       <c r="U25" s="2">
         <v>0</v>
       </c>
-      <c r="V25" s="2">
-        <v>0</v>
-      </c>
-      <c r="W25" s="2">
-        <v>0</v>
-      </c>
-      <c r="X25" s="2">
-        <v>0</v>
-      </c>
       <c r="AF25" s="1">
         <v>0</v>
       </c>
       <c r="BQ25" s="1">
         <v>0</v>
       </c>
-      <c r="BY25" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ25" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA25" s="2">
-        <v>0</v>
-      </c>
       <c r="CB25" s="2">
         <v>0</v>
       </c>
@@ -2846,6 +2837,15 @@
         <v>0</v>
       </c>
       <c r="CR25" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS25" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT25" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU25" s="2">
         <v>0</v>
       </c>
       <c r="CV25" s="1">
@@ -2856,6 +2856,15 @@
       <c r="A26" s="1">
         <v>0</v>
       </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
       <c r="E26" s="2">
         <v>0</v>
       </c>
@@ -2905,15 +2914,6 @@
         <v>0</v>
       </c>
       <c r="U26" s="2">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2">
-        <v>0</v>
-      </c>
-      <c r="W26" s="2">
-        <v>0</v>
-      </c>
-      <c r="X26" s="2">
         <v>0</v>
       </c>
       <c r="AF26" s="1">
@@ -2922,15 +2922,6 @@
       <c r="BQ26" s="1">
         <v>4</v>
       </c>
-      <c r="BY26" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ26" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA26" s="2">
-        <v>0</v>
-      </c>
       <c r="CB26" s="2">
         <v>0</v>
       </c>
@@ -2980,6 +2971,15 @@
         <v>0</v>
       </c>
       <c r="CR26" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS26" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT26" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU26" s="2">
         <v>0</v>
       </c>
       <c r="CV26" s="1">
@@ -2990,6 +2990,15 @@
       <c r="A27" s="1">
         <v>0</v>
       </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
       <c r="E27" s="2">
         <v>0</v>
       </c>
@@ -3041,30 +3050,12 @@
       <c r="U27" s="2">
         <v>0</v>
       </c>
-      <c r="V27" s="2">
-        <v>0</v>
-      </c>
-      <c r="W27" s="2">
-        <v>0</v>
-      </c>
-      <c r="X27" s="2">
-        <v>0</v>
-      </c>
       <c r="AF27" s="1">
         <v>0</v>
       </c>
       <c r="BQ27" s="1">
         <v>0</v>
       </c>
-      <c r="BY27" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ27" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA27" s="2">
-        <v>0</v>
-      </c>
       <c r="CB27" s="2">
         <v>0</v>
       </c>
@@ -3114,6 +3105,15 @@
         <v>0</v>
       </c>
       <c r="CR27" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS27" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT27" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU27" s="2">
         <v>0</v>
       </c>
       <c r="CV27" s="1">
@@ -3124,6 +3124,15 @@
       <c r="A28" s="1">
         <v>0</v>
       </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
       <c r="E28" s="2">
         <v>0</v>
       </c>
@@ -3175,30 +3184,12 @@
       <c r="U28" s="2">
         <v>0</v>
       </c>
-      <c r="V28" s="2">
-        <v>0</v>
-      </c>
-      <c r="W28" s="2">
-        <v>0</v>
-      </c>
-      <c r="X28" s="2">
-        <v>0</v>
-      </c>
       <c r="AF28" s="1">
         <v>0</v>
       </c>
       <c r="BQ28" s="1">
         <v>0</v>
       </c>
-      <c r="BY28" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ28" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA28" s="2">
-        <v>0</v>
-      </c>
       <c r="CB28" s="2">
         <v>0</v>
       </c>
@@ -3248,6 +3239,15 @@
         <v>0</v>
       </c>
       <c r="CR28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT28" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU28" s="2">
         <v>0</v>
       </c>
       <c r="CV28" s="1">
@@ -3258,6 +3258,15 @@
       <c r="A29" s="1">
         <v>0</v>
       </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
       <c r="E29" s="2">
         <v>0</v>
       </c>
@@ -3307,15 +3316,6 @@
         <v>0</v>
       </c>
       <c r="U29" s="2">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2">
-        <v>0</v>
-      </c>
-      <c r="W29" s="2">
-        <v>0</v>
-      </c>
-      <c r="X29" s="2">
         <v>0</v>
       </c>
       <c r="AF29" s="1">
@@ -3324,15 +3324,6 @@
       <c r="BQ29" s="1">
         <v>4</v>
       </c>
-      <c r="BY29" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ29" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA29" s="2">
-        <v>0</v>
-      </c>
       <c r="CB29" s="2">
         <v>0</v>
       </c>
@@ -3382,6 +3373,15 @@
         <v>0</v>
       </c>
       <c r="CR29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT29" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU29" s="2">
         <v>0</v>
       </c>
       <c r="CV29" s="1">
@@ -3392,6 +3392,15 @@
       <c r="A30" s="1">
         <v>0</v>
       </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
       <c r="E30" s="2">
         <v>0</v>
       </c>
@@ -3443,30 +3452,12 @@
       <c r="U30" s="2">
         <v>0</v>
       </c>
-      <c r="V30" s="2">
-        <v>0</v>
-      </c>
-      <c r="W30" s="2">
-        <v>0</v>
-      </c>
-      <c r="X30" s="2">
-        <v>0</v>
-      </c>
       <c r="AF30" s="1">
         <v>0</v>
       </c>
       <c r="BQ30" s="1">
         <v>0</v>
       </c>
-      <c r="BY30" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ30" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA30" s="2">
-        <v>0</v>
-      </c>
       <c r="CB30" s="2">
         <v>0</v>
       </c>
@@ -3516,6 +3507,15 @@
         <v>0</v>
       </c>
       <c r="CR30" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS30" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT30" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU30" s="2">
         <v>0</v>
       </c>
       <c r="CV30" s="1">
@@ -3526,6 +3526,15 @@
       <c r="A31" s="1">
         <v>0</v>
       </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
       <c r="E31" s="2">
         <v>0</v>
       </c>
@@ -3577,30 +3586,12 @@
       <c r="U31" s="2">
         <v>0</v>
       </c>
-      <c r="V31" s="2">
-        <v>0</v>
-      </c>
-      <c r="W31" s="2">
-        <v>0</v>
-      </c>
-      <c r="X31" s="2">
-        <v>0</v>
-      </c>
       <c r="AF31" s="1">
         <v>0</v>
       </c>
       <c r="BQ31" s="1">
         <v>0</v>
       </c>
-      <c r="BY31" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ31" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA31" s="2">
-        <v>0</v>
-      </c>
       <c r="CB31" s="2">
         <v>0</v>
       </c>
@@ -3650,6 +3641,15 @@
         <v>0</v>
       </c>
       <c r="CR31" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS31" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT31" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU31" s="2">
         <v>0</v>
       </c>
       <c r="CV31" s="1">
@@ -3660,6 +3660,15 @@
       <c r="A32" s="1">
         <v>0</v>
       </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
       <c r="E32" s="2">
         <v>0</v>
       </c>
@@ -3709,15 +3718,6 @@
         <v>0</v>
       </c>
       <c r="U32" s="2">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2">
-        <v>0</v>
-      </c>
-      <c r="W32" s="2">
-        <v>0</v>
-      </c>
-      <c r="X32" s="2">
         <v>0</v>
       </c>
       <c r="AF32" s="1">
@@ -3726,15 +3726,6 @@
       <c r="BQ32" s="1">
         <v>4</v>
       </c>
-      <c r="BY32" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ32" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA32" s="2">
-        <v>0</v>
-      </c>
       <c r="CB32" s="2">
         <v>0</v>
       </c>
@@ -3784,6 +3775,15 @@
         <v>0</v>
       </c>
       <c r="CR32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU32" s="2">
         <v>0</v>
       </c>
       <c r="CV32" s="1">
@@ -3794,13 +3794,13 @@
       <c r="A33" s="1">
         <v>0</v>
       </c>
-      <c r="B33" s="4">
-        <v>0</v>
-      </c>
-      <c r="C33" s="4">
-        <v>7</v>
-      </c>
-      <c r="D33" s="4">
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
@@ -3854,30 +3854,12 @@
       <c r="U33" s="2">
         <v>0</v>
       </c>
-      <c r="V33" s="2">
-        <v>0</v>
-      </c>
-      <c r="W33" s="2">
-        <v>0</v>
-      </c>
-      <c r="X33" s="2">
-        <v>0</v>
-      </c>
       <c r="AF33" s="1">
         <v>0</v>
       </c>
       <c r="BQ33" s="1">
         <v>0</v>
       </c>
-      <c r="BY33" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ33" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA33" s="2">
-        <v>0</v>
-      </c>
       <c r="CB33" s="2">
         <v>0</v>
       </c>
@@ -3929,13 +3911,13 @@
       <c r="CR33" s="2">
         <v>0</v>
       </c>
-      <c r="CS33" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT33" s="4">
-        <v>7</v>
-      </c>
-      <c r="CU33" s="4">
+      <c r="CS33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU33" s="2">
         <v>0</v>
       </c>
       <c r="CV33" s="1">
@@ -4118,21 +4100,21 @@
       <c r="A42" s="1">
         <v>0</v>
       </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
       <c r="AF42" s="1">
         <v>0</v>
       </c>
@@ -4199,19 +4181,19 @@
       <c r="BQ42" s="1">
         <v>0</v>
       </c>
-      <c r="BX42" s="3">
-        <v>0</v>
-      </c>
-      <c r="BY42" s="3">
-        <v>0</v>
-      </c>
-      <c r="BZ42" s="3">
-        <v>0</v>
-      </c>
       <c r="CA42" s="3">
         <v>0</v>
       </c>
       <c r="CB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="CC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="CD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="CE42" s="3">
         <v>0</v>
       </c>
       <c r="CV42" s="1">
@@ -4222,21 +4204,21 @@
       <c r="A43" s="1">
         <v>0</v>
       </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
       <c r="AF43" s="1">
         <v>0</v>
       </c>
@@ -4303,19 +4285,19 @@
       <c r="BQ43" s="1">
         <v>0</v>
       </c>
-      <c r="BX43" s="3">
-        <v>0</v>
-      </c>
-      <c r="BY43" s="3">
-        <v>0</v>
-      </c>
-      <c r="BZ43" s="3">
-        <v>0</v>
-      </c>
       <c r="CA43" s="3">
         <v>0</v>
       </c>
       <c r="CB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="CC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="CD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="CE43" s="3">
         <v>0</v>
       </c>
       <c r="CV43" s="1">
@@ -4326,19 +4308,19 @@
       <c r="A44" s="1">
         <v>0</v>
       </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>11</v>
+      </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
       <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3">
-        <v>11</v>
-      </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
         <v>0</v>
       </c>
       <c r="AF44" s="1">
@@ -4407,19 +4389,19 @@
       <c r="BQ44" s="1">
         <v>4</v>
       </c>
-      <c r="BX44" s="3">
-        <v>0</v>
-      </c>
-      <c r="BY44" s="3">
-        <v>0</v>
-      </c>
-      <c r="BZ44" s="3">
+      <c r="CA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="CB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="CC44" s="3">
         <v>11</v>
       </c>
-      <c r="CA44" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB44" s="3">
+      <c r="CD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="CE44" s="3">
         <v>0</v>
       </c>
       <c r="CV44" s="1">
@@ -4430,21 +4412,21 @@
       <c r="A45" s="1">
         <v>0</v>
       </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
       <c r="AF45" s="1">
         <v>0</v>
       </c>
@@ -4511,19 +4493,19 @@
       <c r="BQ45" s="1">
         <v>0</v>
       </c>
-      <c r="BX45" s="3">
-        <v>0</v>
-      </c>
-      <c r="BY45" s="3">
-        <v>0</v>
-      </c>
-      <c r="BZ45" s="3">
-        <v>0</v>
-      </c>
       <c r="CA45" s="3">
         <v>0</v>
       </c>
       <c r="CB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="CC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="CD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="CE45" s="3">
         <v>0</v>
       </c>
       <c r="CV45" s="1">
@@ -4534,21 +4516,21 @@
       <c r="A46" s="1">
         <v>0</v>
       </c>
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
       <c r="U46" s="3">
         <v>0</v>
       </c>
       <c r="V46" s="3">
         <v>0</v>
       </c>
-      <c r="W46" s="3">
-        <v>0</v>
-      </c>
-      <c r="X46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>0</v>
-      </c>
       <c r="AF46" s="4">
         <v>0</v>
       </c>
@@ -4615,19 +4597,19 @@
       <c r="BQ46" s="4">
         <v>0</v>
       </c>
-      <c r="BX46" s="3">
-        <v>0</v>
-      </c>
-      <c r="BY46" s="3">
-        <v>0</v>
-      </c>
-      <c r="BZ46" s="3">
-        <v>0</v>
-      </c>
       <c r="CA46" s="3">
         <v>0</v>
       </c>
       <c r="CB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="CC46" s="3">
+        <v>0</v>
+      </c>
+      <c r="CD46" s="3">
+        <v>0</v>
+      </c>
+      <c r="CE46" s="3">
         <v>0</v>
       </c>
       <c r="CV46" s="1">
@@ -5922,13 +5904,13 @@
       <c r="A68" s="1">
         <v>0</v>
       </c>
-      <c r="B68" s="4">
-        <v>0</v>
-      </c>
-      <c r="C68" s="4">
-        <v>7</v>
-      </c>
-      <c r="D68" s="4">
+      <c r="B68" s="2">
+        <v>0</v>
+      </c>
+      <c r="C68" s="2">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2">
         <v>0</v>
       </c>
       <c r="E68" s="2">
@@ -5980,15 +5962,6 @@
         <v>0</v>
       </c>
       <c r="U68" s="2">
-        <v>0</v>
-      </c>
-      <c r="V68" s="2">
-        <v>0</v>
-      </c>
-      <c r="W68" s="2">
-        <v>0</v>
-      </c>
-      <c r="X68" s="2">
         <v>0</v>
       </c>
       <c r="AF68" s="1">
@@ -5997,15 +5970,6 @@
       <c r="BQ68" s="1">
         <v>4</v>
       </c>
-      <c r="BY68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA68" s="2">
-        <v>0</v>
-      </c>
       <c r="CB68" s="2">
         <v>0</v>
       </c>
@@ -6057,13 +6021,13 @@
       <c r="CR68" s="2">
         <v>0</v>
       </c>
-      <c r="CS68" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT68" s="4">
-        <v>7</v>
-      </c>
-      <c r="CU68" s="4">
+      <c r="CS68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU68" s="2">
         <v>0</v>
       </c>
       <c r="CV68" s="1">
@@ -6074,6 +6038,15 @@
       <c r="A69" s="1">
         <v>0</v>
       </c>
+      <c r="B69" s="2">
+        <v>0</v>
+      </c>
+      <c r="C69" s="2">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2">
+        <v>0</v>
+      </c>
       <c r="E69" s="2">
         <v>0</v>
       </c>
@@ -6125,30 +6098,12 @@
       <c r="U69" s="2">
         <v>0</v>
       </c>
-      <c r="V69" s="2">
-        <v>0</v>
-      </c>
-      <c r="W69" s="2">
-        <v>0</v>
-      </c>
-      <c r="X69" s="2">
-        <v>0</v>
-      </c>
       <c r="AF69" s="1">
         <v>0</v>
       </c>
       <c r="BQ69" s="1">
         <v>0</v>
       </c>
-      <c r="BY69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA69" s="2">
-        <v>0</v>
-      </c>
       <c r="CB69" s="2">
         <v>0</v>
       </c>
@@ -6198,6 +6153,15 @@
         <v>0</v>
       </c>
       <c r="CR69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU69" s="2">
         <v>0</v>
       </c>
       <c r="CV69" s="1">
@@ -6208,6 +6172,15 @@
       <c r="A70" s="1">
         <v>0</v>
       </c>
+      <c r="B70" s="2">
+        <v>0</v>
+      </c>
+      <c r="C70" s="2">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0</v>
+      </c>
       <c r="E70" s="2">
         <v>0</v>
       </c>
@@ -6259,30 +6232,12 @@
       <c r="U70" s="2">
         <v>0</v>
       </c>
-      <c r="V70" s="2">
-        <v>0</v>
-      </c>
-      <c r="W70" s="2">
-        <v>0</v>
-      </c>
-      <c r="X70" s="2">
-        <v>0</v>
-      </c>
       <c r="AF70" s="1">
         <v>0</v>
       </c>
       <c r="BQ70" s="1">
         <v>0</v>
       </c>
-      <c r="BY70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA70" s="2">
-        <v>0</v>
-      </c>
       <c r="CB70" s="2">
         <v>0</v>
       </c>
@@ -6332,6 +6287,15 @@
         <v>0</v>
       </c>
       <c r="CR70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU70" s="2">
         <v>0</v>
       </c>
       <c r="CV70" s="1">
@@ -6342,6 +6306,15 @@
       <c r="A71" s="1">
         <v>0</v>
       </c>
+      <c r="B71" s="2">
+        <v>0</v>
+      </c>
+      <c r="C71" s="2">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0</v>
+      </c>
       <c r="E71" s="2">
         <v>0</v>
       </c>
@@ -6391,15 +6364,6 @@
         <v>0</v>
       </c>
       <c r="U71" s="2">
-        <v>0</v>
-      </c>
-      <c r="V71" s="2">
-        <v>0</v>
-      </c>
-      <c r="W71" s="2">
-        <v>0</v>
-      </c>
-      <c r="X71" s="2">
         <v>0</v>
       </c>
       <c r="AF71" s="1">
@@ -6408,15 +6372,6 @@
       <c r="BQ71" s="1">
         <v>4</v>
       </c>
-      <c r="BY71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA71" s="2">
-        <v>0</v>
-      </c>
       <c r="CB71" s="2">
         <v>0</v>
       </c>
@@ -6466,6 +6421,15 @@
         <v>0</v>
       </c>
       <c r="CR71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU71" s="2">
         <v>0</v>
       </c>
       <c r="CV71" s="1">
@@ -6476,6 +6440,15 @@
       <c r="A72" s="1">
         <v>0</v>
       </c>
+      <c r="B72" s="2">
+        <v>0</v>
+      </c>
+      <c r="C72" s="2">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2">
+        <v>0</v>
+      </c>
       <c r="E72" s="2">
         <v>0</v>
       </c>
@@ -6527,30 +6500,12 @@
       <c r="U72" s="2">
         <v>0</v>
       </c>
-      <c r="V72" s="2">
-        <v>0</v>
-      </c>
-      <c r="W72" s="2">
-        <v>0</v>
-      </c>
-      <c r="X72" s="2">
-        <v>0</v>
-      </c>
       <c r="AF72" s="1">
         <v>0</v>
       </c>
       <c r="BQ72" s="1">
         <v>0</v>
       </c>
-      <c r="BY72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA72" s="2">
-        <v>0</v>
-      </c>
       <c r="CB72" s="2">
         <v>0</v>
       </c>
@@ -6600,6 +6555,15 @@
         <v>0</v>
       </c>
       <c r="CR72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU72" s="2">
         <v>0</v>
       </c>
       <c r="CV72" s="1">
@@ -6610,6 +6574,15 @@
       <c r="A73" s="1">
         <v>0</v>
       </c>
+      <c r="B73" s="2">
+        <v>0</v>
+      </c>
+      <c r="C73" s="2">
+        <v>0</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0</v>
+      </c>
       <c r="E73" s="2">
         <v>0</v>
       </c>
@@ -6661,30 +6634,12 @@
       <c r="U73" s="2">
         <v>0</v>
       </c>
-      <c r="V73" s="2">
-        <v>0</v>
-      </c>
-      <c r="W73" s="2">
-        <v>0</v>
-      </c>
-      <c r="X73" s="2">
-        <v>0</v>
-      </c>
       <c r="AF73" s="1">
         <v>0</v>
       </c>
       <c r="BQ73" s="1">
         <v>0</v>
       </c>
-      <c r="BY73" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ73" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA73" s="2">
-        <v>0</v>
-      </c>
       <c r="CB73" s="2">
         <v>0</v>
       </c>
@@ -6734,6 +6689,15 @@
         <v>0</v>
       </c>
       <c r="CR73" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS73" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT73" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU73" s="2">
         <v>0</v>
       </c>
       <c r="CV73" s="1">
@@ -6744,6 +6708,15 @@
       <c r="A74" s="1">
         <v>0</v>
       </c>
+      <c r="B74" s="2">
+        <v>0</v>
+      </c>
+      <c r="C74" s="2">
+        <v>0</v>
+      </c>
+      <c r="D74" s="2">
+        <v>0</v>
+      </c>
       <c r="E74" s="2">
         <v>0</v>
       </c>
@@ -6793,15 +6766,6 @@
         <v>0</v>
       </c>
       <c r="U74" s="2">
-        <v>0</v>
-      </c>
-      <c r="V74" s="2">
-        <v>0</v>
-      </c>
-      <c r="W74" s="2">
-        <v>0</v>
-      </c>
-      <c r="X74" s="2">
         <v>0</v>
       </c>
       <c r="AF74" s="1">
@@ -6810,15 +6774,6 @@
       <c r="BQ74" s="1">
         <v>4</v>
       </c>
-      <c r="BY74" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ74" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA74" s="2">
-        <v>0</v>
-      </c>
       <c r="CB74" s="2">
         <v>0</v>
       </c>
@@ -6868,6 +6823,15 @@
         <v>0</v>
       </c>
       <c r="CR74" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS74" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT74" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU74" s="2">
         <v>0</v>
       </c>
       <c r="CV74" s="1">
@@ -6878,6 +6842,15 @@
       <c r="A75" s="1">
         <v>0</v>
       </c>
+      <c r="B75" s="2">
+        <v>0</v>
+      </c>
+      <c r="C75" s="2">
+        <v>0</v>
+      </c>
+      <c r="D75" s="2">
+        <v>0</v>
+      </c>
       <c r="E75" s="2">
         <v>0</v>
       </c>
@@ -6929,30 +6902,12 @@
       <c r="U75" s="2">
         <v>0</v>
       </c>
-      <c r="V75" s="2">
-        <v>0</v>
-      </c>
-      <c r="W75" s="2">
-        <v>0</v>
-      </c>
-      <c r="X75" s="2">
-        <v>0</v>
-      </c>
       <c r="AF75" s="1">
         <v>0</v>
       </c>
       <c r="BQ75" s="1">
         <v>0</v>
       </c>
-      <c r="BY75" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ75" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA75" s="2">
-        <v>0</v>
-      </c>
       <c r="CB75" s="2">
         <v>0</v>
       </c>
@@ -7002,6 +6957,15 @@
         <v>0</v>
       </c>
       <c r="CR75" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS75" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT75" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU75" s="2">
         <v>0</v>
       </c>
       <c r="CV75" s="1">
@@ -7012,6 +6976,15 @@
       <c r="A76" s="1">
         <v>0</v>
       </c>
+      <c r="B76" s="2">
+        <v>0</v>
+      </c>
+      <c r="C76" s="2">
+        <v>0</v>
+      </c>
+      <c r="D76" s="2">
+        <v>0</v>
+      </c>
       <c r="E76" s="2">
         <v>0</v>
       </c>
@@ -7063,15 +7036,6 @@
       <c r="U76" s="2">
         <v>0</v>
       </c>
-      <c r="V76" s="2">
-        <v>0</v>
-      </c>
-      <c r="W76" s="2">
-        <v>0</v>
-      </c>
-      <c r="X76" s="2">
-        <v>0</v>
-      </c>
       <c r="AD76" s="3">
         <v>0</v>
       </c>
@@ -7102,15 +7066,6 @@
       <c r="BS76" s="3">
         <v>0</v>
       </c>
-      <c r="BY76" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ76" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA76" s="2">
-        <v>0</v>
-      </c>
       <c r="CB76" s="2">
         <v>0</v>
       </c>
@@ -7160,6 +7115,15 @@
         <v>0</v>
       </c>
       <c r="CR76" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS76" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT76" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU76" s="2">
         <v>0</v>
       </c>
       <c r="CV76" s="1">
@@ -7170,6 +7134,15 @@
       <c r="A77" s="1">
         <v>0</v>
       </c>
+      <c r="B77" s="2">
+        <v>0</v>
+      </c>
+      <c r="C77" s="2">
+        <v>0</v>
+      </c>
+      <c r="D77" s="2">
+        <v>0</v>
+      </c>
       <c r="E77" s="2">
         <v>0</v>
       </c>
@@ -7192,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M77" s="2">
         <v>0</v>
@@ -7201,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P77" s="2">
         <v>0</v>
@@ -7221,15 +7194,6 @@
       <c r="U77" s="2">
         <v>0</v>
       </c>
-      <c r="V77" s="2">
-        <v>0</v>
-      </c>
-      <c r="W77" s="2">
-        <v>0</v>
-      </c>
-      <c r="X77" s="2">
-        <v>0</v>
-      </c>
       <c r="AD77" s="3">
         <v>0</v>
       </c>
@@ -7260,15 +7224,6 @@
       <c r="BS77" s="3">
         <v>0</v>
       </c>
-      <c r="BY77" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ77" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA77" s="2">
-        <v>0</v>
-      </c>
       <c r="CB77" s="2">
         <v>0</v>
       </c>
@@ -7291,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="CI77" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CJ77" s="2">
         <v>0</v>
@@ -7300,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="CL77" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CM77" s="2">
         <v>0</v>
@@ -7318,6 +7273,15 @@
         <v>0</v>
       </c>
       <c r="CR77" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS77" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT77" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU77" s="2">
         <v>0</v>
       </c>
       <c r="CV77" s="1">
@@ -7328,6 +7292,15 @@
       <c r="A78" s="1">
         <v>0</v>
       </c>
+      <c r="B78" s="2">
+        <v>0</v>
+      </c>
+      <c r="C78" s="2">
+        <v>0</v>
+      </c>
+      <c r="D78" s="2">
+        <v>0</v>
+      </c>
       <c r="E78" s="2">
         <v>0</v>
       </c>
@@ -7377,15 +7350,6 @@
         <v>0</v>
       </c>
       <c r="U78" s="2">
-        <v>0</v>
-      </c>
-      <c r="V78" s="2">
-        <v>0</v>
-      </c>
-      <c r="W78" s="2">
-        <v>0</v>
-      </c>
-      <c r="X78" s="2">
         <v>0</v>
       </c>
       <c r="AD78" s="3">
@@ -7472,15 +7436,6 @@
       <c r="BS78" s="3">
         <v>0</v>
       </c>
-      <c r="BY78" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ78" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA78" s="2">
-        <v>0</v>
-      </c>
       <c r="CB78" s="2">
         <v>0</v>
       </c>
@@ -7530,6 +7485,15 @@
         <v>0</v>
       </c>
       <c r="CR78" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS78" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT78" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU78" s="2">
         <v>0</v>
       </c>
       <c r="CV78" s="1">
@@ -7540,6 +7504,15 @@
       <c r="A79" s="1">
         <v>0</v>
       </c>
+      <c r="B79" s="2">
+        <v>0</v>
+      </c>
+      <c r="C79" s="2">
+        <v>0</v>
+      </c>
+      <c r="D79" s="2">
+        <v>0</v>
+      </c>
       <c r="E79" s="2">
         <v>0</v>
       </c>
@@ -7591,15 +7564,6 @@
       <c r="U79" s="2">
         <v>0</v>
       </c>
-      <c r="V79" s="2">
-        <v>0</v>
-      </c>
-      <c r="W79" s="2">
-        <v>0</v>
-      </c>
-      <c r="X79" s="2">
-        <v>0</v>
-      </c>
       <c r="AD79" s="3">
         <v>0</v>
       </c>
@@ -7630,15 +7594,6 @@
       <c r="BS79" s="3">
         <v>0</v>
       </c>
-      <c r="BY79" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ79" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA79" s="2">
-        <v>0</v>
-      </c>
       <c r="CB79" s="2">
         <v>0</v>
       </c>
@@ -7688,6 +7643,15 @@
         <v>0</v>
       </c>
       <c r="CR79" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS79" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT79" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU79" s="2">
         <v>0</v>
       </c>
       <c r="CV79" s="1">
@@ -7698,6 +7662,15 @@
       <c r="A80" s="1">
         <v>0</v>
       </c>
+      <c r="B80" s="2">
+        <v>0</v>
+      </c>
+      <c r="C80" s="2">
+        <v>0</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0</v>
+      </c>
       <c r="E80" s="2">
         <v>0</v>
       </c>
@@ -7749,15 +7722,6 @@
       <c r="U80" s="2">
         <v>0</v>
       </c>
-      <c r="V80" s="2">
-        <v>0</v>
-      </c>
-      <c r="W80" s="2">
-        <v>0</v>
-      </c>
-      <c r="X80" s="2">
-        <v>0</v>
-      </c>
       <c r="AD80" s="3">
         <v>0</v>
       </c>
@@ -7788,15 +7752,6 @@
       <c r="BS80" s="3">
         <v>0</v>
       </c>
-      <c r="BY80" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ80" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA80" s="2">
-        <v>0</v>
-      </c>
       <c r="CB80" s="2">
         <v>0</v>
       </c>
@@ -7846,6 +7801,15 @@
         <v>0</v>
       </c>
       <c r="CR80" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS80" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT80" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU80" s="2">
         <v>0</v>
       </c>
       <c r="CV80" s="1">
@@ -7856,6 +7820,15 @@
       <c r="A81" s="1">
         <v>0</v>
       </c>
+      <c r="B81" s="2">
+        <v>0</v>
+      </c>
+      <c r="C81" s="2">
+        <v>0</v>
+      </c>
+      <c r="D81" s="2">
+        <v>0</v>
+      </c>
       <c r="E81" s="2">
         <v>0</v>
       </c>
@@ -7907,24 +7880,6 @@
       <c r="U81" s="2">
         <v>0</v>
       </c>
-      <c r="V81" s="2">
-        <v>0</v>
-      </c>
-      <c r="W81" s="2">
-        <v>0</v>
-      </c>
-      <c r="X81" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY81" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ81" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA81" s="2">
-        <v>0</v>
-      </c>
       <c r="CB81" s="2">
         <v>0</v>
       </c>
@@ -7974,6 +7929,15 @@
         <v>0</v>
       </c>
       <c r="CR81" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS81" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT81" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU81" s="2">
         <v>0</v>
       </c>
       <c r="CV81" s="1">
@@ -7984,6 +7948,15 @@
       <c r="A82" s="1">
         <v>0</v>
       </c>
+      <c r="B82" s="2">
+        <v>0</v>
+      </c>
+      <c r="C82" s="2">
+        <v>0</v>
+      </c>
+      <c r="D82" s="2">
+        <v>0</v>
+      </c>
       <c r="E82" s="2">
         <v>0</v>
       </c>
@@ -8035,24 +8008,6 @@
       <c r="U82" s="2">
         <v>0</v>
       </c>
-      <c r="V82" s="2">
-        <v>0</v>
-      </c>
-      <c r="W82" s="2">
-        <v>0</v>
-      </c>
-      <c r="X82" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY82" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ82" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA82" s="2">
-        <v>0</v>
-      </c>
       <c r="CB82" s="2">
         <v>0</v>
       </c>
@@ -8102,6 +8057,15 @@
         <v>0</v>
       </c>
       <c r="CR82" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS82" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT82" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU82" s="2">
         <v>0</v>
       </c>
       <c r="CV82" s="1">
@@ -8112,6 +8076,15 @@
       <c r="A83" s="1">
         <v>0</v>
       </c>
+      <c r="B83" s="2">
+        <v>0</v>
+      </c>
+      <c r="C83" s="2">
+        <v>0</v>
+      </c>
+      <c r="D83" s="2">
+        <v>0</v>
+      </c>
       <c r="E83" s="2">
         <v>0</v>
       </c>
@@ -8163,24 +8136,6 @@
       <c r="U83" s="2">
         <v>0</v>
       </c>
-      <c r="V83" s="2">
-        <v>0</v>
-      </c>
-      <c r="W83" s="2">
-        <v>0</v>
-      </c>
-      <c r="X83" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY83" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ83" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA83" s="2">
-        <v>0</v>
-      </c>
       <c r="CB83" s="2">
         <v>0</v>
       </c>
@@ -8230,6 +8185,15 @@
         <v>0</v>
       </c>
       <c r="CR83" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS83" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT83" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU83" s="2">
         <v>0</v>
       </c>
       <c r="CV83" s="1">
@@ -8240,6 +8204,15 @@
       <c r="A84" s="1">
         <v>0</v>
       </c>
+      <c r="B84" s="2">
+        <v>0</v>
+      </c>
+      <c r="C84" s="2">
+        <v>0</v>
+      </c>
+      <c r="D84" s="2">
+        <v>0</v>
+      </c>
       <c r="E84" s="2">
         <v>0</v>
       </c>
@@ -8291,24 +8264,6 @@
       <c r="U84" s="2">
         <v>0</v>
       </c>
-      <c r="V84" s="2">
-        <v>0</v>
-      </c>
-      <c r="W84" s="2">
-        <v>0</v>
-      </c>
-      <c r="X84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY84" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ84" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA84" s="2">
-        <v>0</v>
-      </c>
       <c r="CB84" s="2">
         <v>0</v>
       </c>
@@ -8358,6 +8313,15 @@
         <v>0</v>
       </c>
       <c r="CR84" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS84" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT84" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU84" s="2">
         <v>0</v>
       </c>
       <c r="CV84" s="1">
@@ -8368,6 +8332,15 @@
       <c r="A85" s="1">
         <v>0</v>
       </c>
+      <c r="B85" s="2">
+        <v>0</v>
+      </c>
+      <c r="C85" s="2">
+        <v>0</v>
+      </c>
+      <c r="D85" s="2">
+        <v>0</v>
+      </c>
       <c r="E85" s="2">
         <v>0</v>
       </c>
@@ -8419,24 +8392,6 @@
       <c r="U85" s="2">
         <v>0</v>
       </c>
-      <c r="V85" s="2">
-        <v>0</v>
-      </c>
-      <c r="W85" s="2">
-        <v>0</v>
-      </c>
-      <c r="X85" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY85" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ85" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA85" s="2">
-        <v>0</v>
-      </c>
       <c r="CB85" s="2">
         <v>0</v>
       </c>
@@ -8486,6 +8441,15 @@
         <v>0</v>
       </c>
       <c r="CR85" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS85" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT85" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU85" s="2">
         <v>0</v>
       </c>
       <c r="CV85" s="1">
@@ -8496,6 +8460,15 @@
       <c r="A86" s="1">
         <v>0</v>
       </c>
+      <c r="B86" s="2">
+        <v>0</v>
+      </c>
+      <c r="C86" s="2">
+        <v>0</v>
+      </c>
+      <c r="D86" s="2">
+        <v>0</v>
+      </c>
       <c r="E86" s="2">
         <v>0</v>
       </c>
@@ -8547,15 +8520,6 @@
       <c r="U86" s="2">
         <v>0</v>
       </c>
-      <c r="V86" s="2">
-        <v>0</v>
-      </c>
-      <c r="W86" s="2">
-        <v>0</v>
-      </c>
-      <c r="X86" s="2">
-        <v>0</v>
-      </c>
       <c r="AS86" s="3">
         <v>0</v>
       </c>
@@ -8586,15 +8550,6 @@
       <c r="BE86" s="3">
         <v>0</v>
       </c>
-      <c r="BY86" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ86" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA86" s="2">
-        <v>0</v>
-      </c>
       <c r="CB86" s="2">
         <v>0</v>
       </c>
@@ -8644,6 +8599,15 @@
         <v>0</v>
       </c>
       <c r="CR86" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS86" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT86" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU86" s="2">
         <v>0</v>
       </c>
       <c r="CV86" s="1">
@@ -8654,6 +8618,15 @@
       <c r="A87" s="1">
         <v>0</v>
       </c>
+      <c r="B87" s="2">
+        <v>0</v>
+      </c>
+      <c r="C87" s="2">
+        <v>0</v>
+      </c>
+      <c r="D87" s="2">
+        <v>0</v>
+      </c>
       <c r="E87" s="2">
         <v>0</v>
       </c>
@@ -8705,15 +8678,6 @@
       <c r="U87" s="2">
         <v>0</v>
       </c>
-      <c r="V87" s="2">
-        <v>0</v>
-      </c>
-      <c r="W87" s="2">
-        <v>0</v>
-      </c>
-      <c r="X87" s="2">
-        <v>0</v>
-      </c>
       <c r="AS87" s="3">
         <v>0</v>
       </c>
@@ -8744,15 +8708,6 @@
       <c r="BE87" s="3">
         <v>0</v>
       </c>
-      <c r="BY87" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ87" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA87" s="2">
-        <v>0</v>
-      </c>
       <c r="CB87" s="2">
         <v>0</v>
       </c>
@@ -8802,6 +8757,15 @@
         <v>0</v>
       </c>
       <c r="CR87" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS87" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT87" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU87" s="2">
         <v>0</v>
       </c>
       <c r="CV87" s="1">
@@ -8812,7 +8776,7 @@
       <c r="A88" s="1">
         <v>0</v>
       </c>
-      <c r="S88" s="1">
+      <c r="N88" s="1">
         <v>0</v>
       </c>
       <c r="AS88" s="3">
@@ -8854,7 +8818,7 @@
       <c r="BE88" s="3">
         <v>0</v>
       </c>
-      <c r="CD88" s="1">
+      <c r="CI88" s="1">
         <v>0</v>
       </c>
       <c r="CV88" s="1">
@@ -8865,7 +8829,7 @@
       <c r="A89" s="1">
         <v>0</v>
       </c>
-      <c r="S89" s="1">
+      <c r="N89" s="1">
         <v>4</v>
       </c>
       <c r="AS89" s="3">
@@ -8898,7 +8862,7 @@
       <c r="BE89" s="3">
         <v>0</v>
       </c>
-      <c r="CD89" s="1">
+      <c r="CI89" s="1">
         <v>4</v>
       </c>
       <c r="CV89" s="1">
@@ -8909,7 +8873,7 @@
       <c r="A90" s="1">
         <v>0</v>
       </c>
-      <c r="S90" s="1">
+      <c r="N90" s="1">
         <v>0</v>
       </c>
       <c r="AS90" s="3">
@@ -8942,7 +8906,7 @@
       <c r="BE90" s="3">
         <v>0</v>
       </c>
-      <c r="CD90" s="1">
+      <c r="CI90" s="1">
         <v>0</v>
       </c>
       <c r="CV90" s="1">
@@ -8953,7 +8917,7 @@
       <c r="A91" s="1">
         <v>0</v>
       </c>
-      <c r="S91" s="1">
+      <c r="N91" s="4">
         <v>0</v>
       </c>
       <c r="AU91" s="1">
@@ -8962,7 +8926,7 @@
       <c r="BC91" s="1">
         <v>0</v>
       </c>
-      <c r="CD91" s="1">
+      <c r="CI91" s="4">
         <v>0</v>
       </c>
       <c r="CV91" s="1">
@@ -8973,8 +8937,8 @@
       <c r="A92" s="1">
         <v>0</v>
       </c>
-      <c r="S92" s="1">
-        <v>4</v>
+      <c r="N92" s="4">
+        <v>8</v>
       </c>
       <c r="AU92" s="1">
         <v>4</v>
@@ -8982,8 +8946,8 @@
       <c r="BC92" s="1">
         <v>4</v>
       </c>
-      <c r="CD92" s="1">
-        <v>4</v>
+      <c r="CI92" s="4">
+        <v>8</v>
       </c>
       <c r="CV92" s="1">
         <v>0</v>
@@ -8993,7 +8957,7 @@
       <c r="A93" s="1">
         <v>0</v>
       </c>
-      <c r="S93" s="1">
+      <c r="N93" s="4">
         <v>0</v>
       </c>
       <c r="AU93" s="1">
@@ -9002,7 +8966,7 @@
       <c r="BC93" s="1">
         <v>0</v>
       </c>
-      <c r="CD93" s="1">
+      <c r="CI93" s="4">
         <v>0</v>
       </c>
       <c r="CV93" s="1">
@@ -9013,7 +8977,7 @@
       <c r="A94" s="1">
         <v>0</v>
       </c>
-      <c r="S94" s="1">
+      <c r="N94" s="4">
         <v>0</v>
       </c>
       <c r="AU94" s="1">
@@ -9022,7 +8986,7 @@
       <c r="BC94" s="1">
         <v>0</v>
       </c>
-      <c r="CD94" s="1">
+      <c r="CI94" s="4">
         <v>0</v>
       </c>
       <c r="CV94" s="1">
@@ -9033,8 +8997,8 @@
       <c r="A95" s="1">
         <v>0</v>
       </c>
-      <c r="S95" s="1">
-        <v>4</v>
+      <c r="N95" s="4">
+        <v>8</v>
       </c>
       <c r="AU95" s="1">
         <v>4</v>
@@ -9042,8 +9006,8 @@
       <c r="BC95" s="1">
         <v>4</v>
       </c>
-      <c r="CD95" s="1">
-        <v>4</v>
+      <c r="CI95" s="4">
+        <v>8</v>
       </c>
       <c r="CV95" s="1">
         <v>0</v>
@@ -9053,7 +9017,7 @@
       <c r="B96" s="1">
         <v>6</v>
       </c>
-      <c r="S96" s="1">
+      <c r="N96" s="4">
         <v>0</v>
       </c>
       <c r="AU96" s="1">
@@ -9062,7 +9026,7 @@
       <c r="BC96" s="1">
         <v>0</v>
       </c>
-      <c r="CD96" s="1">
+      <c r="CI96" s="4">
         <v>0</v>
       </c>
       <c r="CU96" s="1">
@@ -9073,7 +9037,7 @@
       <c r="C97" s="1">
         <v>0</v>
       </c>
-      <c r="S97" s="1">
+      <c r="N97" s="1">
         <v>0</v>
       </c>
       <c r="AU97" s="1">
@@ -9082,7 +9046,7 @@
       <c r="BC97" s="1">
         <v>0</v>
       </c>
-      <c r="CD97" s="1">
+      <c r="CI97" s="1">
         <v>0</v>
       </c>
       <c r="CT97" s="1">
@@ -9093,7 +9057,7 @@
       <c r="D98" s="1">
         <v>0</v>
       </c>
-      <c r="S98" s="1">
+      <c r="N98" s="1">
         <v>4</v>
       </c>
       <c r="AU98" s="1">
@@ -9102,7 +9066,7 @@
       <c r="BC98" s="1">
         <v>4</v>
       </c>
-      <c r="CD98" s="1">
+      <c r="CI98" s="1">
         <v>4</v>
       </c>
       <c r="CS98" s="1">
@@ -9113,7 +9077,7 @@
       <c r="E99" s="1">
         <v>6</v>
       </c>
-      <c r="S99" s="1">
+      <c r="N99" s="1">
         <v>0</v>
       </c>
       <c r="AU99" s="1">
@@ -9122,7 +9086,7 @@
       <c r="BC99" s="1">
         <v>0</v>
       </c>
-      <c r="CD99" s="1">
+      <c r="CI99" s="1">
         <v>0</v>
       </c>
       <c r="CR99" s="1">
